--- a/data/trans_orig/P29-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P29-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92636</t>
+          <t>90908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130009</t>
+          <t>129068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97714</t>
+          <t>98306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132637</t>
+          <t>132286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200410</t>
+          <t>198728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251514</t>
+          <t>249623</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60092</t>
+          <t>58809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91889</t>
+          <t>90424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50375</t>
+          <t>49212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78460</t>
+          <t>77125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117902</t>
+          <t>118054</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160756</t>
+          <t>161211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>264283</t>
+          <t>269387</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>308547</t>
+          <t>312360</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112145</t>
+          <t>110161</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146275</t>
+          <t>143798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>390549</t>
+          <t>387098</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>444839</t>
+          <t>443957</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69825</t>
+          <t>71435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103700</t>
+          <t>105405</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>133761</t>
+          <t>134027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171904</t>
+          <t>172183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215733</t>
+          <t>214265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>266831</t>
+          <t>265494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>44246</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72759</t>
+          <t>74406</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>51648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80218</t>
+          <t>80197</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>102212</t>
+          <t>101816</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>142233</t>
+          <t>142206</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203839</t>
+          <t>203157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242423</t>
+          <t>241241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135967</t>
+          <t>134054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175046</t>
+          <t>172193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>349929</t>
+          <t>348393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>406262</t>
+          <t>403419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109930</t>
+          <t>110872</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151971</t>
+          <t>151536</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50234</t>
+          <t>51712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75454</t>
+          <t>75009</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>167840</t>
+          <t>168135</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>216417</t>
+          <t>215862</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57573</t>
+          <t>57335</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90949</t>
+          <t>90235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33098</t>
+          <t>32538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55933</t>
+          <t>56010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95802</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135572</t>
+          <t>136875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315365</t>
+          <t>317117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360218</t>
+          <t>360730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50360</t>
+          <t>49930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75554</t>
+          <t>74164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>375296</t>
+          <t>374589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>428274</t>
+          <t>426133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>300007</t>
+          <t>302762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>362176</t>
+          <t>365108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>320003</t>
+          <t>319074</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>371970</t>
+          <t>371867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>631152</t>
+          <t>632283</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>718482</t>
+          <t>721721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209407</t>
+          <t>211279</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264766</t>
+          <t>264920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153517</t>
+          <t>153642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198878</t>
+          <t>197457</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377338</t>
+          <t>377480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>450408</t>
+          <t>449222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>632718</t>
+          <t>633465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>705666</t>
+          <t>702598</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>169811</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>219200</t>
+          <t>217476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>820433</t>
+          <t>817913</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>907081</t>
+          <t>905416</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76551</t>
+          <t>76970</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111436</t>
+          <t>111202</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290954</t>
+          <t>291560</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>339609</t>
+          <t>339409</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>380841</t>
+          <t>379416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>441469</t>
+          <t>441363</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>30696</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52866</t>
+          <t>55759</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93938</t>
+          <t>93745</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>131519</t>
+          <t>131030</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>133171</t>
+          <t>132203</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>175525</t>
+          <t>176559</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197599</t>
+          <t>197165</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234310</t>
+          <t>235082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119749</t>
+          <t>120157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161571</t>
+          <t>163043</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>327948</t>
+          <t>325825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>388564</t>
+          <t>384485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83114</t>
+          <t>83203</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>114788</t>
+          <t>113307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>763270</t>
+          <t>758995</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>827091</t>
+          <t>825137</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>854380</t>
+          <t>856203</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>930044</t>
+          <t>930519</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,15%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48315</t>
+          <t>47834</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73163</t>
+          <t>73508</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>211619</t>
+          <t>211980</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>263479</t>
+          <t>265204</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>266871</t>
+          <t>269376</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>328605</t>
+          <t>324835</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123047</t>
+          <t>122845</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155899</t>
+          <t>156540</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>194497</t>
+          <t>190505</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>245249</t>
+          <t>245063</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>327856</t>
+          <t>327483</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>392708</t>
+          <t>390986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>804664</t>
+          <t>803963</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>902790</t>
+          <t>903305</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1725998</t>
+          <t>1726105</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1846321</t>
+          <t>1844870</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2554543</t>
+          <t>2554848</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2713078</t>
+          <t>2718877</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>503036</t>
+          <t>500259</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>585443</t>
+          <t>588122</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>651803</t>
+          <t>651958</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>750235</t>
+          <t>742566</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1174932</t>
+          <t>1172725</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1299398</t>
+          <t>1302077</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1816700</t>
+          <t>1815804</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1933473</t>
+          <t>1931198</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>842036</t>
+          <t>847672</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>951465</t>
+          <t>948540</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2694738</t>
+          <t>2687776</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2855511</t>
+          <t>2865874</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64559</t>
+          <t>63822</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98405</t>
+          <t>96925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110159</t>
+          <t>109264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146307</t>
+          <t>145902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180846</t>
+          <t>181579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232921</t>
+          <t>234286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48642</t>
+          <t>48815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81935</t>
+          <t>81798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>28256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52379</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83473</t>
+          <t>83820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123579</t>
+          <t>124630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>271741</t>
+          <t>271922</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>313124</t>
+          <t>312806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130598</t>
+          <t>129305</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>166598</t>
+          <t>167035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>412000</t>
+          <t>412863</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>469567</t>
+          <t>471122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88296</t>
+          <t>88409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127921</t>
+          <t>128069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>136943</t>
+          <t>137527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174800</t>
+          <t>177104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>233986</t>
+          <t>234768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>291614</t>
+          <t>292066</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43859</t>
+          <t>43792</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75089</t>
+          <t>74130</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52491</t>
+          <t>53941</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79923</t>
+          <t>78748</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118446</t>
+          <t>116734</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>230651</t>
+          <t>234549</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>274165</t>
+          <t>277048</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124349</t>
+          <t>121357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162861</t>
+          <t>160972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>369963</t>
+          <t>368581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>429914</t>
+          <t>426994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136296</t>
+          <t>138339</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>183003</t>
+          <t>183950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130669</t>
+          <t>130397</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163106</t>
+          <t>162952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>281400</t>
+          <t>276712</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>338230</t>
+          <t>336993</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64502</t>
+          <t>64678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98788</t>
+          <t>100106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23880</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45074</t>
+          <t>45990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94970</t>
+          <t>95135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137032</t>
+          <t>137177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>362547</t>
+          <t>360196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>414030</t>
+          <t>413342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63311</t>
+          <t>64296</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94994</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>437845</t>
+          <t>437232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>495797</t>
+          <t>496473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>320750</t>
+          <t>315461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>383798</t>
+          <t>379213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>383690</t>
+          <t>381876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>441339</t>
+          <t>441087</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>717842</t>
+          <t>714997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>805037</t>
+          <t>806381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123369</t>
+          <t>124691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169531</t>
+          <t>170927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102168</t>
+          <t>100974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143993</t>
+          <t>143310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240225</t>
+          <t>239615</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301521</t>
+          <t>301934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>627209</t>
+          <t>628385</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>697452</t>
+          <t>698037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>205671</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257804</t>
+          <t>258622</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>846765</t>
+          <t>847835</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>940855</t>
+          <t>939890</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133183</t>
+          <t>134499</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174961</t>
+          <t>175374</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>452608</t>
+          <t>454242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>508967</t>
+          <t>507713</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>598636</t>
+          <t>598711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>673900</t>
+          <t>670630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40735</t>
+          <t>39227</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67642</t>
+          <t>68370</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77047</t>
+          <t>77923</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113826</t>
+          <t>114006</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>121924</t>
+          <t>124584</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170072</t>
+          <t>171183</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>280959</t>
+          <t>283557</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>326502</t>
+          <t>326356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162716</t>
+          <t>163086</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213212</t>
+          <t>213030</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>453330</t>
+          <t>457376</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>526336</t>
+          <t>528282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>76761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>107863</t>
+          <t>108202</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>662791</t>
+          <t>666449</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>727675</t>
+          <t>727564</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>747270</t>
+          <t>750990</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>824502</t>
+          <t>830672</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>47517</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128012</t>
+          <t>126642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>171441</t>
+          <t>172160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160636</t>
+          <t>159840</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211017</t>
+          <t>210610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122972</t>
+          <t>123152</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154754</t>
+          <t>154928</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>235605</t>
+          <t>236702</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>292171</t>
+          <t>293240</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>369413</t>
+          <t>367716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>439792</t>
+          <t>437263</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>893229</t>
+          <t>886582</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1001345</t>
+          <t>997213</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1955811</t>
+          <t>1957342</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2075416</t>
+          <t>2076615</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2873091</t>
+          <t>2866765</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3044578</t>
+          <t>3037327</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>396994</t>
+          <t>397381</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>478181</t>
+          <t>482407</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>437713</t>
+          <t>437421</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>523188</t>
+          <t>520920</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>860314</t>
+          <t>850422</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>972221</t>
+          <t>972887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1982285</t>
+          <t>1985134</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2102527</t>
+          <t>2104982</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>996853</t>
+          <t>1003931</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1109832</t>
+          <t>1111796</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3007841</t>
+          <t>3015806</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3182804</t>
+          <t>3182948</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46601</t>
+          <t>47530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48665</t>
+          <t>47791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76996</t>
+          <t>76028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77915</t>
+          <t>75779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112954</t>
+          <t>114572</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88089</t>
+          <t>88102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125071</t>
+          <t>125901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113590</t>
+          <t>111090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149386</t>
+          <t>147207</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>211494</t>
+          <t>210747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>262366</t>
+          <t>263069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269550</t>
+          <t>269026</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>309645</t>
+          <t>310915</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134809</t>
+          <t>135067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172680</t>
+          <t>172572</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>413439</t>
+          <t>415202</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>472820</t>
+          <t>472467</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>44511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50344</t>
+          <t>49320</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80297</t>
+          <t>80387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77930</t>
+          <t>79112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114458</t>
+          <t>115335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90846</t>
+          <t>89309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127074</t>
+          <t>124070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>99550</t>
+          <t>99781</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>137782</t>
+          <t>136403</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>199760</t>
+          <t>199362</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>249551</t>
+          <t>248068</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>220339</t>
+          <t>219909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>257796</t>
+          <t>257031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170010</t>
+          <t>170878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211903</t>
+          <t>212013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>402122</t>
+          <t>403290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>457194</t>
+          <t>457193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43427</t>
+          <t>43708</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71964</t>
+          <t>72083</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39543</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65325</t>
+          <t>65949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89441</t>
+          <t>91178</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129521</t>
+          <t>129932</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109076</t>
+          <t>107552</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149125</t>
+          <t>149266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44590</t>
+          <t>44249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70836</t>
+          <t>68967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161829</t>
+          <t>163990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209568</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315879</t>
+          <t>314065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358635</t>
+          <t>357891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43660</t>
+          <t>44444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69917</t>
+          <t>69642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366784</t>
+          <t>365220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>418425</t>
+          <t>415784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133039</t>
+          <t>131840</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180190</t>
+          <t>179915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208911</t>
+          <t>206108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>260433</t>
+          <t>258955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>355903</t>
+          <t>348360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>428464</t>
+          <t>424981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302982</t>
+          <t>305338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>364884</t>
+          <t>366255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,82 +9081,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>31,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>292659</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>264163</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>319153</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>35,44%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>38,64%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>627409</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>587201</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>669886</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>31,77%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>292659</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>266716</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>320492</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>32,29%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>38,81%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>627409</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>586789</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>668724</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>31,77%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>628097</t>
+          <t>627045</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>694418</t>
+          <t>690744</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>273079</t>
+          <t>272739</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>325773</t>
+          <t>330076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>914708</t>
+          <t>914363</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1004207</t>
+          <t>1006206</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77874</t>
+          <t>75356</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113681</t>
+          <t>110196</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232910</t>
+          <t>230057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>287146</t>
+          <t>284568</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>318402</t>
+          <t>317982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>383010</t>
+          <t>384534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>187322</t>
+          <t>188136</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>236575</t>
+          <t>235440</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257377</t>
+          <t>261016</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>313545</t>
+          <t>317156</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>463761</t>
+          <t>460419</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>535213</t>
+          <t>534139</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>289993</t>
+          <t>291576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>340173</t>
+          <t>339651</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167385</t>
+          <t>168119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>214007</t>
+          <t>214631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>471368</t>
+          <t>471028</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>543050</t>
+          <t>544516</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43811</t>
+          <t>45451</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>72894</t>
+          <t>73869</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>413792</t>
+          <t>411423</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>481454</t>
+          <t>483088</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>468338</t>
+          <t>473303</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>542277</t>
+          <t>548090</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51760</t>
+          <t>52166</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80386</t>
+          <t>80865</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>346747</t>
+          <t>345810</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>409413</t>
+          <t>408253</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>405244</t>
+          <t>406138</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>477587</t>
+          <t>478987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145101</t>
+          <t>145566</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>180549</t>
+          <t>179709</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>230359</t>
+          <t>228773</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>289145</t>
+          <t>286370</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>384140</t>
+          <t>386578</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>452547</t>
+          <t>450976</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>385276</t>
+          <t>391496</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>465610</t>
+          <t>467221</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1063619</t>
+          <t>1062446</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1176358</t>
+          <t>1177882</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1473258</t>
+          <t>1478183</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1615921</t>
+          <t>1617684</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>905145</t>
+          <t>900691</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1011311</t>
+          <t>1004643</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1202194</t>
+          <t>1198607</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1316650</t>
+          <t>1316530</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2139764</t>
+          <t>2130657</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2295779</t>
+          <t>2289680</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1944892</t>
+          <t>1945997</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2062878</t>
+          <t>2062821</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1095726</t>
+          <t>1092282</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1206122</t>
+          <t>1200781</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3055373</t>
+          <t>3070003</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3226535</t>
+          <t>3237391</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>48038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77823</t>
+          <t>77982</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91359</t>
+          <t>90258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121609</t>
+          <t>119912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146997</t>
+          <t>146454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190604</t>
+          <t>188762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84703</t>
+          <t>83655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121748</t>
+          <t>119836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108176</t>
+          <t>107241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140542</t>
+          <t>139045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198347</t>
+          <t>199984</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248175</t>
+          <t>246267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>320814</t>
+          <t>320517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>364199</t>
+          <t>363839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>199812</t>
+          <t>201686</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>237410</t>
+          <t>237553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>532170</t>
+          <t>532630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>592165</t>
+          <t>592148</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>56593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88390</t>
+          <t>86212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64958</t>
+          <t>64092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90354</t>
+          <t>90293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127843</t>
+          <t>128134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168315</t>
+          <t>168475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>101789</t>
+          <t>103001</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>143983</t>
+          <t>143094</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96158</t>
+          <t>98532</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128286</t>
+          <t>129199</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>210767</t>
+          <t>209037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>262642</t>
+          <t>258371</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>233483</t>
+          <t>236311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>280031</t>
+          <t>278369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174317</t>
+          <t>173941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210019</t>
+          <t>206455</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>423336</t>
+          <t>423887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>477850</t>
+          <t>477669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122749</t>
+          <t>122724</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>46168</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65290</t>
+          <t>65414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55246</t>
+          <t>60682</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>188225</t>
+          <t>188041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37161</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>164494</t>
+          <t>167486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41734</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60332</t>
+          <t>61980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58676</t>
+          <t>68434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219920</t>
+          <t>218969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>386612</t>
+          <t>383585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>605640</t>
+          <t>594522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50860</t>
+          <t>50603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70180</t>
+          <t>70909</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431639</t>
+          <t>433483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719272</t>
+          <t>701477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131398</t>
+          <t>130402</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175823</t>
+          <t>177699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>300963</t>
+          <t>302550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>274382</t>
+          <t>264730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>440788</t>
+          <t>439149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>244093</t>
+          <t>241735</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>307132</t>
+          <t>304819</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141683</t>
+          <t>125689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>320595</t>
+          <t>319144</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367704</t>
+          <t>369698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>594751</t>
+          <t>592109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>563977</t>
+          <t>567124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>637599</t>
+          <t>636071</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>363061</t>
+          <t>360525</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>705858</t>
+          <t>734653</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>984932</t>
+          <t>985673</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1361112</t>
+          <t>1361768</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>52689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83124</t>
+          <t>80774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211736</t>
+          <t>213075</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>335124</t>
+          <t>337077</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>283043</t>
+          <t>286415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412600</t>
+          <t>413016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>120774</t>
+          <t>119576</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>164379</t>
+          <t>161129</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>212756</t>
+          <t>223715</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>335994</t>
+          <t>336555</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>351705</t>
+          <t>363633</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>476718</t>
+          <t>479828</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>243740</t>
+          <t>244970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>288386</t>
+          <t>290208</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>211380</t>
+          <t>208601</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>424035</t>
+          <t>418861</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>477156</t>
+          <t>480545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>679438</t>
+          <t>675619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33741</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77958</t>
+          <t>78443</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>266813</t>
+          <t>267563</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>316392</t>
+          <t>317120</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>309600</t>
+          <t>310163</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>377856</t>
+          <t>377071</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53196</t>
+          <t>54937</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100350</t>
+          <t>101311</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>249217</t>
+          <t>251478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>300118</t>
+          <t>301093</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>318765</t>
+          <t>315228</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>388954</t>
+          <t>384487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84612</t>
+          <t>86415</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137943</t>
+          <t>140108</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>170775</t>
+          <t>170996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220310</t>
+          <t>221298</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>268645</t>
+          <t>268829</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>343936</t>
+          <t>343127</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>363834</t>
+          <t>366862</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>536128</t>
+          <t>534217</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>835075</t>
+          <t>849673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1135274</t>
+          <t>1131323</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1284352</t>
+          <t>1318354</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1626996</t>
+          <t>1630578</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>620000</t>
+          <t>595224</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>896655</t>
+          <t>896597</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>904647</t>
+          <t>889566</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1199706</t>
+          <t>1201087</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1638742</t>
+          <t>1668018</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2055512</t>
+          <t>2055139</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1958252</t>
+          <t>1958729</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2393408</t>
+          <t>2405989</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1264064</t>
+          <t>1262717</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1837795</t>
+          <t>1840301</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3281223</t>
+          <t>3282155</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4027320</t>
+          <t>3984338</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P29-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P29-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90908</t>
+          <t>91627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129068</t>
+          <t>129903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98306</t>
+          <t>98138</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132286</t>
+          <t>131534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198728</t>
+          <t>198980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249623</t>
+          <t>252000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58809</t>
+          <t>60890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90424</t>
+          <t>91561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49212</t>
+          <t>50333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77125</t>
+          <t>78100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118054</t>
+          <t>117602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161211</t>
+          <t>160184</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269387</t>
+          <t>269225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>312360</t>
+          <t>312364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110161</t>
+          <t>111644</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143798</t>
+          <t>145509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>387098</t>
+          <t>388708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>443957</t>
+          <t>445196</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71435</t>
+          <t>70673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105405</t>
+          <t>105336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134027</t>
+          <t>132147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172183</t>
+          <t>171713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214265</t>
+          <t>215893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>265494</t>
+          <t>268240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44246</t>
+          <t>44477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74406</t>
+          <t>72956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51648</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80197</t>
+          <t>80930</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101816</t>
+          <t>101593</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>142206</t>
+          <t>141537</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203157</t>
+          <t>201964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241241</t>
+          <t>242459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134054</t>
+          <t>135224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172193</t>
+          <t>173602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348393</t>
+          <t>349749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>403419</t>
+          <t>405813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110872</t>
+          <t>112865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151536</t>
+          <t>151535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51712</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75009</t>
+          <t>76091</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>168135</t>
+          <t>168281</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>215862</t>
+          <t>219354</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57335</t>
+          <t>58972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90235</t>
+          <t>90170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32538</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>56127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>98942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136875</t>
+          <t>138703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317117</t>
+          <t>316147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360730</t>
+          <t>362241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49930</t>
+          <t>49364</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74164</t>
+          <t>75356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>374589</t>
+          <t>372970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>426133</t>
+          <t>427968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>302762</t>
+          <t>303334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>365108</t>
+          <t>368959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>319074</t>
+          <t>317544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>371867</t>
+          <t>372084</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>632283</t>
+          <t>637215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>721721</t>
+          <t>722593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>211279</t>
+          <t>208091</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264920</t>
+          <t>261272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153642</t>
+          <t>152844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197457</t>
+          <t>199909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377480</t>
+          <t>378482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>449222</t>
+          <t>450733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>633465</t>
+          <t>635184</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>702598</t>
+          <t>702958</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>169811</t>
+          <t>170225</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>217476</t>
+          <t>218920</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>817913</t>
+          <t>821432</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>905416</t>
+          <t>908825</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76970</t>
+          <t>76942</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>110371</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>291560</t>
+          <t>294278</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>339409</t>
+          <t>339956</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>379416</t>
+          <t>377213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>441363</t>
+          <t>439232</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30696</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55759</t>
+          <t>54156</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93745</t>
+          <t>92253</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>131030</t>
+          <t>131454</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>132203</t>
+          <t>132792</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>176559</t>
+          <t>179403</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197165</t>
+          <t>197082</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235082</t>
+          <t>234357</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120157</t>
+          <t>119775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163043</t>
+          <t>162014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>325825</t>
+          <t>324340</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>384485</t>
+          <t>386159</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83203</t>
+          <t>82796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113307</t>
+          <t>114143</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>758995</t>
+          <t>759935</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>825137</t>
+          <t>824478</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>856203</t>
+          <t>853298</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>930519</t>
+          <t>929478</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47834</t>
+          <t>46810</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73508</t>
+          <t>74013</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>211980</t>
+          <t>208346</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>265204</t>
+          <t>264242</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>269376</t>
+          <t>268659</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>324835</t>
+          <t>326642</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122845</t>
+          <t>123269</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>156540</t>
+          <t>155966</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>190505</t>
+          <t>193959</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>245063</t>
+          <t>244373</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>327483</t>
+          <t>327891</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>390986</t>
+          <t>395369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>803963</t>
+          <t>801926</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>903305</t>
+          <t>905487</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1726105</t>
+          <t>1725742</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1844870</t>
+          <t>1838553</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2554848</t>
+          <t>2555683</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2718877</t>
+          <t>2722008</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>500259</t>
+          <t>500321</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>588122</t>
+          <t>584017</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>651958</t>
+          <t>651783</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>742566</t>
+          <t>741858</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1172725</t>
+          <t>1172934</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1302077</t>
+          <t>1309217</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1815804</t>
+          <t>1819052</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1931198</t>
+          <t>1934585</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>847672</t>
+          <t>847185</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>948540</t>
+          <t>948848</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2687776</t>
+          <t>2692873</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2865874</t>
+          <t>2854129</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63822</t>
+          <t>63654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96925</t>
+          <t>96649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109264</t>
+          <t>106484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145902</t>
+          <t>145732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>181579</t>
+          <t>181632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234286</t>
+          <t>232850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48815</t>
+          <t>49513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81798</t>
+          <t>80768</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>28679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>53688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83820</t>
+          <t>84043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124630</t>
+          <t>124853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>271922</t>
+          <t>274153</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>312806</t>
+          <t>313599</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129305</t>
+          <t>131116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167035</t>
+          <t>169542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>412863</t>
+          <t>414787</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>471122</t>
+          <t>471453</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>87160</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128069</t>
+          <t>126773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137527</t>
+          <t>134313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177104</t>
+          <t>174174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>234275</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>292066</t>
+          <t>289117</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43792</t>
+          <t>42840</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74130</t>
+          <t>73496</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>28793</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53941</t>
+          <t>52539</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78748</t>
+          <t>81155</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>116734</t>
+          <t>119552</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>234549</t>
+          <t>233380</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>277048</t>
+          <t>276542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121357</t>
+          <t>124194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160972</t>
+          <t>163115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>368581</t>
+          <t>368265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>426994</t>
+          <t>427773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,52%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138339</t>
+          <t>139513</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>183950</t>
+          <t>184388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130397</t>
+          <t>130265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162952</t>
+          <t>164488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>276712</t>
+          <t>280296</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>336993</t>
+          <t>336855</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64678</t>
+          <t>65883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100106</t>
+          <t>100286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45990</t>
+          <t>45872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95135</t>
+          <t>94365</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137177</t>
+          <t>135142</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360196</t>
+          <t>361984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>413342</t>
+          <t>411952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64296</t>
+          <t>65402</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95410</t>
+          <t>97823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>437232</t>
+          <t>438076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>496473</t>
+          <t>498916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>315461</t>
+          <t>318370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>379213</t>
+          <t>380747</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>381876</t>
+          <t>383998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>441087</t>
+          <t>441672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>714997</t>
+          <t>717064</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>806381</t>
+          <t>809471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124691</t>
+          <t>124811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170927</t>
+          <t>172628</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100974</t>
+          <t>101140</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143310</t>
+          <t>145118</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239615</t>
+          <t>236695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301934</t>
+          <t>299870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>628385</t>
+          <t>626038</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>698037</t>
+          <t>696532</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>203243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258622</t>
+          <t>256453</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>847835</t>
+          <t>846543</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>939890</t>
+          <t>938752</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,77%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134499</t>
+          <t>133154</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175374</t>
+          <t>174804</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>454242</t>
+          <t>452803</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>507713</t>
+          <t>507283</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>598711</t>
+          <t>599433</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>670630</t>
+          <t>673115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39227</t>
+          <t>39335</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68370</t>
+          <t>67674</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77923</t>
+          <t>75633</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114006</t>
+          <t>113527</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124584</t>
+          <t>125722</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>171183</t>
+          <t>172239</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>283557</t>
+          <t>280743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>326356</t>
+          <t>326891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163086</t>
+          <t>162655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213030</t>
+          <t>212272</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>457376</t>
+          <t>453361</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>528282</t>
+          <t>527759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76761</t>
+          <t>77704</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108202</t>
+          <t>109340</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>666449</t>
+          <t>662143</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>727564</t>
+          <t>727693</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>750990</t>
+          <t>748939</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>830672</t>
+          <t>828338</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>25750</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47517</t>
+          <t>47397</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126642</t>
+          <t>125993</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>172160</t>
+          <t>170593</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159840</t>
+          <t>159707</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>210610</t>
+          <t>213205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123152</t>
+          <t>122096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154928</t>
+          <t>154694</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>236702</t>
+          <t>233955</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>293240</t>
+          <t>293449</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>367716</t>
+          <t>368382</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>437263</t>
+          <t>438859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>886582</t>
+          <t>887898</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>997213</t>
+          <t>995306</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1957342</t>
+          <t>1951836</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2076615</t>
+          <t>2080591</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2866765</t>
+          <t>2873676</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3037327</t>
+          <t>3044677</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>397381</t>
+          <t>398665</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>482407</t>
+          <t>481855</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>437421</t>
+          <t>437456</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>520920</t>
+          <t>517778</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>850422</t>
+          <t>851071</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>972887</t>
+          <t>970918</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1985134</t>
+          <t>1985513</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2104982</t>
+          <t>2103110</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1003931</t>
+          <t>1003276</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1111796</t>
+          <t>1114157</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3015806</t>
+          <t>3006243</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3182948</t>
+          <t>3179005</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>24134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47530</t>
+          <t>46909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47791</t>
+          <t>48035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>76890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75779</t>
+          <t>75202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114572</t>
+          <t>116038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88102</t>
+          <t>88559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125901</t>
+          <t>125064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111090</t>
+          <t>112914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147207</t>
+          <t>148321</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210747</t>
+          <t>211021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>263069</t>
+          <t>264065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269026</t>
+          <t>268488</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>310915</t>
+          <t>309153</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135067</t>
+          <t>136004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172572</t>
+          <t>174033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>415202</t>
+          <t>414872</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>472467</t>
+          <t>473023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,11%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>44962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49320</t>
+          <t>50874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80387</t>
+          <t>80256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79112</t>
+          <t>74884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115335</t>
+          <t>112922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89309</t>
+          <t>89189</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124070</t>
+          <t>125456</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>99781</t>
+          <t>99367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136403</t>
+          <t>137101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>199362</t>
+          <t>198328</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>248068</t>
+          <t>250026</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>219909</t>
+          <t>220488</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>257031</t>
+          <t>258751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170878</t>
+          <t>171896</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>212013</t>
+          <t>211207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>403290</t>
+          <t>403760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>457193</t>
+          <t>459993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,37%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72083</t>
+          <t>74680</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40052</t>
+          <t>40075</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65949</t>
+          <t>65509</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91178</t>
+          <t>90201</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129932</t>
+          <t>130066</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107552</t>
+          <t>110761</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149266</t>
+          <t>149324</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44249</t>
+          <t>45134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68967</t>
+          <t>69689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163990</t>
+          <t>160597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>211257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>312565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357891</t>
+          <t>357978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44444</t>
+          <t>44090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69642</t>
+          <t>69516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>365220</t>
+          <t>363498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>415784</t>
+          <t>416634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>133491</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179915</t>
+          <t>178591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>206108</t>
+          <t>208967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258955</t>
+          <t>261975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348360</t>
+          <t>353785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424981</t>
+          <t>425692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>305338</t>
+          <t>305741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>366255</t>
+          <t>365681</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264163</t>
+          <t>264646</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319153</t>
+          <t>319672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>587201</t>
+          <t>586023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>669886</t>
+          <t>669939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>627045</t>
+          <t>625743</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>690744</t>
+          <t>690859</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>272739</t>
+          <t>271399</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>330076</t>
+          <t>326565</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>914363</t>
+          <t>916481</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1006206</t>
+          <t>1006467</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75356</t>
+          <t>76615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110196</t>
+          <t>113350</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230057</t>
+          <t>232976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>284568</t>
+          <t>284759</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>317982</t>
+          <t>315729</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384534</t>
+          <t>384896</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>188136</t>
+          <t>187219</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>235440</t>
+          <t>235279</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>261016</t>
+          <t>261020</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>317156</t>
+          <t>313928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>460419</t>
+          <t>460145</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>534139</t>
+          <t>533786</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>291576</t>
+          <t>289337</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>339651</t>
+          <t>341721</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168119</t>
+          <t>168749</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>214631</t>
+          <t>216115</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>471028</t>
+          <t>470820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>544516</t>
+          <t>545194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45451</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>75252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>411423</t>
+          <t>417082</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>483088</t>
+          <t>483302</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>473303</t>
+          <t>471115</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>548090</t>
+          <t>546410</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52166</t>
+          <t>51187</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80865</t>
+          <t>79339</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>345810</t>
+          <t>342475</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>408253</t>
+          <t>408457</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>406138</t>
+          <t>410665</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>478987</t>
+          <t>479486</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145566</t>
+          <t>145119</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179709</t>
+          <t>179923</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>228773</t>
+          <t>226694</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>286370</t>
+          <t>288295</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>386578</t>
+          <t>385634</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>450976</t>
+          <t>455517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>391496</t>
+          <t>389617</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>467221</t>
+          <t>467824</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1062446</t>
+          <t>1063021</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1177882</t>
+          <t>1171709</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1478183</t>
+          <t>1462836</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1617684</t>
+          <t>1609983</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>900691</t>
+          <t>903587</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1004643</t>
+          <t>1005644</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1198607</t>
+          <t>1199390</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1316530</t>
+          <t>1312980</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2130657</t>
+          <t>2136429</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2289680</t>
+          <t>2287478</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1945997</t>
+          <t>1942032</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2062821</t>
+          <t>2061272</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1092282</t>
+          <t>1096741</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1200781</t>
+          <t>1209118</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3070003</t>
+          <t>3064104</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3237391</t>
+          <t>3235129</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60940</t>
+          <t>69565</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48038</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77982</t>
+          <t>84144</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>105375</t>
+          <t>116404</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90258</t>
+          <t>101013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119912</t>
+          <t>133701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>166315</t>
+          <t>185968</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146454</t>
+          <t>163025</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188762</t>
+          <t>209417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>101316</t>
+          <t>110570</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83655</t>
+          <t>92659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119836</t>
+          <t>131769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>122625</t>
+          <t>134911</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107241</t>
+          <t>117882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139045</t>
+          <t>152774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>223941</t>
+          <t>245482</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>199984</t>
+          <t>219770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246267</t>
+          <t>273107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>342956</t>
+          <t>370483</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>320517</t>
+          <t>346786</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>363839</t>
+          <t>392518</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>219467</t>
+          <t>237096</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>201686</t>
+          <t>217252</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>237553</t>
+          <t>255237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>562423</t>
+          <t>607579</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>532630</t>
+          <t>578065</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>592148</t>
+          <t>635250</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70649</t>
+          <t>76692</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56593</t>
+          <t>62350</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>93662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77159</t>
+          <t>89572</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>75858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90293</t>
+          <t>104483</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>147808</t>
+          <t>166263</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128134</t>
+          <t>147003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168475</t>
+          <t>189135</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>122251</t>
+          <t>131284</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>103001</t>
+          <t>110222</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>143094</t>
+          <t>152413</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>112515</t>
+          <t>122521</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98532</t>
+          <t>108320</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>129199</t>
+          <t>140895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>234766</t>
+          <t>253806</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>209037</t>
+          <t>229290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>258371</t>
+          <t>279448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>259313</t>
+          <t>275236</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>236311</t>
+          <t>251418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>278369</t>
+          <t>297126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>191590</t>
+          <t>209594</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>173941</t>
+          <t>189944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206455</t>
+          <t>226228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>450903</t>
+          <t>484830</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>423887</t>
+          <t>455675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>477669</t>
+          <t>510554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>381264</t>
+          <t>421687</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381264</t>
+          <t>421687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381264</t>
+          <t>421687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>833477</t>
+          <t>904899</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>833477</t>
+          <t>904899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833477</t>
+          <t>904899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72717</t>
+          <t>89179</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29135</t>
+          <t>72449</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122724</t>
+          <t>106935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55274</t>
+          <t>60666</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46168</t>
+          <t>50140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>72539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>127992</t>
+          <t>149845</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60682</t>
+          <t>130855</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>188041</t>
+          <t>171125</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>99581</t>
+          <t>108423</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41477</t>
+          <t>91114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167486</t>
+          <t>128463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50749</t>
+          <t>56681</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41896</t>
+          <t>46907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61980</t>
+          <t>68085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>150330</t>
+          <t>165104</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68434</t>
+          <t>143898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218969</t>
+          <t>188167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>495965</t>
+          <t>274011</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>383585</t>
+          <t>251103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>594522</t>
+          <t>294279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60101</t>
+          <t>69120</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50603</t>
+          <t>57659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70909</t>
+          <t>80969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>556066</t>
+          <t>343130</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>433483</t>
+          <t>317968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>701477</t>
+          <t>368446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166124</t>
+          <t>186467</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166124</t>
+          <t>186467</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166124</t>
+          <t>186467</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834388</t>
+          <t>658079</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834388</t>
+          <t>658079</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834388</t>
+          <t>658079</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>152497</t>
+          <t>183342</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130402</t>
+          <t>158425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177699</t>
+          <t>210337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>231727</t>
+          <t>264842</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117083</t>
+          <t>242687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>302550</t>
+          <t>288466</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>384224</t>
+          <t>448184</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264730</t>
+          <t>414386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>439149</t>
+          <t>487839</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>274349</t>
+          <t>298003</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>241735</t>
+          <t>269617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>304819</t>
+          <t>332414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>246458</t>
+          <t>274066</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125689</t>
+          <t>250825</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319144</t>
+          <t>296936</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>520807</t>
+          <t>572070</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369698</t>
+          <t>532181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>592109</t>
+          <t>612836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>603577</t>
+          <t>645958</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>567124</t>
+          <t>608923</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>636071</t>
+          <t>682050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>498337</t>
+          <t>320620</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>360525</t>
+          <t>295658</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>734653</t>
+          <t>344621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1101914</t>
+          <t>966579</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>985673</t>
+          <t>920019</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1361768</t>
+          <t>1011688</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1030422</t>
+          <t>1127303</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1030422</t>
+          <t>1127303</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1030422</t>
+          <t>1127303</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>976523</t>
+          <t>859529</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>976523</t>
+          <t>859529</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>976523</t>
+          <t>859529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2006945</t>
+          <t>1986833</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2006945</t>
+          <t>1986833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2006945</t>
+          <t>1986833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>66747</t>
+          <t>116176</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52689</t>
+          <t>97743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80774</t>
+          <t>139295</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>271583</t>
+          <t>276382</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213075</t>
+          <t>254546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337077</t>
+          <t>297468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>338330</t>
+          <t>392559</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>286415</t>
+          <t>363689</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>413016</t>
+          <t>423439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>139767</t>
+          <t>153258</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119576</t>
+          <t>132591</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>161129</t>
+          <t>175729</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>294371</t>
+          <t>319486</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>223715</t>
+          <t>298952</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>336555</t>
+          <t>342254</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>434138</t>
+          <t>472744</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>363633</t>
+          <t>442339</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>479828</t>
+          <t>507084</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>266735</t>
+          <t>296694</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244970</t>
+          <t>272098</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>290208</t>
+          <t>322141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>271701</t>
+          <t>232804</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208601</t>
+          <t>212141</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>418861</t>
+          <t>254179</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>538437</t>
+          <t>529498</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>480545</t>
+          <t>498226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>675619</t>
+          <t>562464</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473249</t>
+          <t>566128</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>473249</t>
+          <t>566128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>473249</t>
+          <t>566128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>837656</t>
+          <t>828672</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>837656</t>
+          <t>828672</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>837656</t>
+          <t>828672</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1310905</t>
+          <t>1394800</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1310905</t>
+          <t>1394800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1310905</t>
+          <t>1394800</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>52563</t>
+          <t>57757</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>39225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78443</t>
+          <t>82039</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>290724</t>
+          <t>334584</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>267563</t>
+          <t>307900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>317120</t>
+          <t>362996</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>343287</t>
+          <t>392341</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>310163</t>
+          <t>359266</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>377071</t>
+          <t>431201</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>75911</t>
+          <t>76652</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54937</t>
+          <t>56129</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101311</t>
+          <t>99680</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>275447</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>251478</t>
+          <t>274640</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>301093</t>
+          <t>327919</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>351357</t>
+          <t>380319</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>315228</t>
+          <t>348307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>384487</t>
+          <t>416499</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>112033</t>
+          <t>102818</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86415</t>
+          <t>78763</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>140108</t>
+          <t>126192</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>193366</t>
+          <t>204004</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>170996</t>
+          <t>179876</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>221298</t>
+          <t>230629</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>305399</t>
+          <t>306822</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>268829</t>
+          <t>273496</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>343127</t>
+          <t>346539</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>759536</t>
+          <t>842255</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>759536</t>
+          <t>842255</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>759536</t>
+          <t>842255</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1000043</t>
+          <t>1079482</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1000043</t>
+          <t>1079482</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1000043</t>
+          <t>1079482</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>476113</t>
+          <t>592710</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>366862</t>
+          <t>540013</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>534217</t>
+          <t>644232</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1031842</t>
+          <t>1142450</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>849673</t>
+          <t>1092068</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1131323</t>
+          <t>1190812</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1507955</t>
+          <t>1735160</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1318354</t>
+          <t>1667921</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1630578</t>
+          <t>1805269</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>813174</t>
+          <t>878191</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>595224</t>
+          <t>827504</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>896597</t>
+          <t>934995</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1102166</t>
+          <t>1211333</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>889566</t>
+          <t>1163151</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1201087</t>
+          <t>1262426</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1915340</t>
+          <t>2089523</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1668018</t>
+          <t>2010215</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2055139</t>
+          <t>2169142</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2080580</t>
+          <t>1965200</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1958729</t>
+          <t>1902477</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2405989</t>
+          <t>2029910</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1434561</t>
+          <t>1273238</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1262717</t>
+          <t>1222593</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1840301</t>
+          <t>1327559</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3515141</t>
+          <t>3238438</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3282155</t>
+          <t>3155930</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3984338</t>
+          <t>3321184</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3369867</t>
+          <t>3436101</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3369867</t>
+          <t>3436101</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3369867</t>
+          <t>3436101</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3568569</t>
+          <t>3627021</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3568569</t>
+          <t>3627021</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3568569</t>
+          <t>3627021</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6938436</t>
+          <t>7063122</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6938436</t>
+          <t>7063122</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6938436</t>
+          <t>7063122</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
